--- a/沃尔玛产品信息表.xlsx
+++ b/沃尔玛产品信息表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>标题</t>
   </si>
@@ -57,19 +57,6 @@
   </si>
   <si>
     <t>Brand: REDCAMP | Product Dimensions: 114"L x 114"W x 78"H | Item Weight: 9.5 Pounds | Floor Width: 9.5 Feet | Recommended Uses For Product: Camping &amp; Hiking | Occupancy: 6 Person | Seasons: 3 Season | Water Resistance Technology: Silver glue coating | Special Feature: UV Protection | Occupant Capacity: 6</t>
-  </si>
-  <si>
-    <t>REDCAMP 39 Inch Outdoor Bar Table, Folding Paito Bar Height Table with Waterproof Mesh Top for Balcony, Garden, Hot Tub, Poolside, Indoor, Rectangle Black</t>
-  </si>
-  <si>
-    <t>Spacious and Sturdy: Measuring 39x16", our outdoor bar table offers ample storage space for all your essentials while supporting up to 440lbs, perfect for gatherings or as a sleek hot tub table for your outdoor relaxation.
-Electrophoresis Technique: The surface of the hot tub table adopts special electrophoresis technique which can make the table rust-proof, corrosion resistant and easy-to-clean. Mesh desktop doesn't accumulate dust and water, making it easy to maintain.
-Stable Structure &amp; Perfect Height: The reinforced crossbar under the side table increase the whole stability of the table. You can also rest your feet on the brackets to have a coffee enjoy. The bar top is designed at t he perfect height to free your arms and elbows.
-Portable and Space-Saving: This high pub table is designed for convenience with foldable legs and included Velcro straps for compact storage. Carrying it is a breeze thanks to the integrated handle, making it perfect for parties, picnics, or any event.
-Versatile Indoor and Outdoor Use: Ideal for both indoor and outdoor settings, this bar table enhances your dining experiences at restaurants, bars, bistros, coffee shops, or kitchens and is equally perfect for patios, balconies, yards, and poolside lounging.</t>
-  </si>
-  <si>
-    <t>Brand: REDCAMP | Product Dimensions: 39"D x 16"W x 36"H | Item Weight: 15 Pounds | Maximum Weight Recommendation: 352 Pounds | Frame Material: Iron</t>
   </si>
   <si>
     <t>Elevate Your Canopy Experience: Transform your standard pop-up canopy into a sheltered, private, and versatile living space. This inner tent attachment is the perfect add-on to enhance your protection against sun, wind, and light rain. Please ensure you have a 10x10 ft or 10x20 ft straight-leg canopy before ordering.
@@ -1195,8 +1182,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="30" style="7" customWidth="1"/>
     <col min="2" max="2" width="90" style="7" customWidth="1"/>
@@ -1240,35 +1227,18 @@
     </row>
     <row r="3" ht="100" customHeight="1" spans="1:5">
       <c r="A3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="D3">
-        <v>45485</v>
+        <v>453244</v>
       </c>
       <c r="E3">
-        <v>24563343</v>
-      </c>
-    </row>
-    <row r="4" ht="100" customHeight="1" spans="1:5">
-      <c r="A4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>453244</v>
-      </c>
-      <c r="E4">
         <v>235345346</v>
       </c>
     </row>
@@ -1290,37 +1260,37 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="45" customHeight="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="45" customHeight="1" spans="1:1">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="100" customHeight="1" spans="1:1">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="45" customHeight="1" spans="1:1">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="45" customHeight="1" spans="1:1">
       <c r="A5" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="45" customHeight="1" spans="1:1">
       <c r="A6" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:1">
       <c r="A7" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
